--- a/photography_forms/002_host_event_legal_release_authorization--photography_forms.xlsx
+++ b/photography_forms/002_host_event_legal_release_authorization--photography_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -763,7 +763,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>event_host_name</t>
+          <t>event_host_name_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>photographer_name</t>
+          <t>photographer_name_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Photographer</t>
+          <t>Photographer Name 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -929,7 +929,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Event Host</t>
+          <t>Event Host (2)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -993,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>event_host_address</t>
+          <t>event_host_address_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Event Host Address</t>
+          <t>Event Host Address 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
